--- a/교재/엑셀교재v2/020-021_찾기참조함수_실습.xlsx
+++ b/교재/엑셀교재v2/020-021_찾기참조함수_실습.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CompUse2nd\교재\엑셀교재v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014C19D1-E0D3-4DA0-B2A1-F2742CA8BEB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB52E94-B301-4A18-850F-73390001F8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24255" yWindow="810" windowWidth="22200" windowHeight="14790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="찾기참조_실습" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="130">
   <si>
     <t>제품코드</t>
   </si>
@@ -131,310 +131,308 @@
     <t>배태지</t>
   </si>
   <si>
+    <t>B-1</t>
+  </si>
+  <si>
+    <t>이용석</t>
+  </si>
+  <si>
+    <t>a의 위치 SEARCH</t>
+  </si>
+  <si>
+    <t>이효리</t>
+  </si>
+  <si>
+    <t>a의 위치 FIND</t>
+  </si>
+  <si>
+    <t>3월 소고기 등급별 판매 통계</t>
+  </si>
+  <si>
+    <t>등급별 kg당 판매가</t>
+  </si>
+  <si>
+    <t>지점명</t>
+  </si>
+  <si>
+    <t>3월 판매량 (kg)</t>
+  </si>
+  <si>
+    <t>월간 판매액 (원)</t>
+  </si>
+  <si>
+    <t>금액 (원)</t>
+  </si>
+  <si>
+    <t>횡성점</t>
+  </si>
+  <si>
+    <t>국산(A++)</t>
+  </si>
+  <si>
+    <t>이천점</t>
+  </si>
+  <si>
+    <t>국산(A+)</t>
+  </si>
+  <si>
+    <t>보령점</t>
+  </si>
+  <si>
+    <t>국산(A)</t>
+  </si>
+  <si>
+    <t>제주점</t>
+  </si>
+  <si>
+    <t>미국산</t>
+  </si>
+  <si>
+    <t>부산점</t>
+  </si>
+  <si>
+    <t>호주산</t>
+  </si>
+  <si>
+    <t>3월 판매량이 가장 많은 지점</t>
+  </si>
+  <si>
+    <t>학습용 전사 자료: 노트 020~021페이지. SEARCH는 M12, FIND는 M13에 입력합니다.</t>
+  </si>
+  <si>
+    <t>판매사원 이름은 사진의 판독에 따라 옮겼으며, 이 문제의 계산에는 사용하지 않습니다.</t>
+  </si>
+  <si>
+    <t>파란 칸은 정답 수식입니다. 셀을 클릭하면 수식 입력줄에서 수식을 볼 수 있습니다.</t>
+  </si>
+  <si>
+    <t>020 021 찾기 참조 함수 문제와 힌트</t>
+  </si>
+  <si>
+    <t>실습 시트에서 입력하고 정답 시트와 비교하세요. 단가·등급·비고는 13행까지 채웁니다.</t>
+  </si>
+  <si>
+    <t>번호</t>
+  </si>
+  <si>
+    <t>입력 위치</t>
+  </si>
+  <si>
+    <t>문제</t>
+  </si>
+  <si>
+    <t>힌트</t>
+  </si>
+  <si>
+    <t>첫 결과</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>G3:G13</t>
+  </si>
+  <si>
+    <t>제품코드 첫 글자로 단가를 구하세요.</t>
+  </si>
+  <si>
+    <t>VLOOKUP, LEFT</t>
+  </si>
+  <si>
+    <t>G3=10,000</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>H3:H13</t>
+  </si>
+  <si>
+    <t>점수에 따른 등급을 구하세요.</t>
+  </si>
+  <si>
+    <t>HLOOKUP, 근사값 1</t>
+  </si>
+  <si>
+    <t>H3=A</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>I3:I13</t>
+  </si>
+  <si>
+    <t>제품코드 끝 숫자가 1~4이면 슈퍼·골드·실버·브론즈를 표시하세요.</t>
+  </si>
+  <si>
+    <t>CHOOSE, RIGHT</t>
+  </si>
+  <si>
+    <t>I3=슈퍼</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>K11에서 소문자 a의 위치를 대소문자 구분 없이 구하세요.</t>
+  </si>
+  <si>
+    <t>SEARCH</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>K11에서 소문자 a의 위치를 대소문자를 구분하여 구하세요.</t>
+  </si>
+  <si>
+    <t>FIND</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>E18:E22</t>
+  </si>
+  <si>
+    <t>판매량 × 등급별 kg당 판매가를 구하세요.</t>
+  </si>
+  <si>
+    <t>INDEX, MATCH</t>
+  </si>
+  <si>
+    <t>E18=11,720,000</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>B25</t>
+  </si>
+  <si>
+    <t>3월 판매량이 가장 많은 지점명을 구하세요.</t>
+  </si>
+  <si>
+    <t>INDEX, MATCH, LARGE</t>
+  </si>
+  <si>
+    <t>입력 방법: 이름 상자에 G3 입력 → Enter → =로 시작하는 수식 입력 → Enter.</t>
+  </si>
+  <si>
+    <t>채우기 방법: G3:G13 선택 → 홈 → 편집 → 채우기 → 아래쪽 또는 Ctrl+D.</t>
+  </si>
+  <si>
+    <t>함수 마법사: 결과 셀 선택 → 수식 → 함수 삽입 또는 수식 입력줄 왼쪽 fx.</t>
+  </si>
+  <si>
+    <t>범위 고정: 수식 편집 중 K3:L6 선택 → F4 → $K$3:$L$6.</t>
+  </si>
+  <si>
+    <t>INDEX의 범위는 제목을 뺀 데이터입니다. MATCH의 0은 정확히 같은 값을 찾습니다.</t>
+  </si>
+  <si>
+    <t>원본 문제 ⑤의 M12는 화면 배치에 맞춰 M13으로 수정했습니다.</t>
+  </si>
+  <si>
+    <t>정답은 직접 계산하는 수식으로 저장되어 입력 자료를 바꾸면 결과도 바뀝니다.</t>
+  </si>
+  <si>
+    <t>추가 연습과 확인</t>
+  </si>
+  <si>
+    <t>연습 내용</t>
+  </si>
+  <si>
+    <t>답 입력</t>
+  </si>
+  <si>
+    <t>확인할 내용</t>
+  </si>
+  <si>
+    <t>79점의 등급</t>
+  </si>
+  <si>
+    <t>실습 시트의 점수 기준표를 HLOOKUP으로 참조</t>
+  </si>
+  <si>
+    <t>D-4의 단가</t>
+  </si>
+  <si>
+    <t>LEFT로 첫 글자를 구한 뒤 VLOOKUP 사용</t>
+  </si>
+  <si>
+    <t>D-4의 비고</t>
+  </si>
+  <si>
+    <t>RIGHT로 끝 숫자를 구한 뒤 CHOOSE 사용</t>
+  </si>
+  <si>
+    <t>두 번째 판매량 지점</t>
+  </si>
+  <si>
+    <t>LARGE의 두 번째 인수를 2로 사용</t>
+  </si>
+  <si>
+    <t>점수 60의 등급</t>
+  </si>
+  <si>
+    <t>HLOOKUP 근사값의 경계값 확인</t>
+  </si>
+  <si>
+    <t>문항</t>
+  </si>
+  <si>
+    <t>정답 수식</t>
+  </si>
+  <si>
+    <t>결과</t>
+  </si>
+  <si>
+    <t>79점</t>
+  </si>
+  <si>
+    <t>=HLOOKUP(79,'찾기참조_실습'!$L$8:$P$9,2,1)</t>
+  </si>
+  <si>
+    <t>D-4 단가</t>
+  </si>
+  <si>
+    <t>=VLOOKUP(LEFT("D-4",1),'찾기참조_실습'!$K$3:$L$6,2,0)</t>
+  </si>
+  <si>
+    <t>D-4 비고</t>
+  </si>
+  <si>
+    <t>=CHOOSE(RIGHT("D-4",1),"슈퍼","골드","실버","브론즈")</t>
+  </si>
+  <si>
+    <t>두 번째 지점</t>
+  </si>
+  <si>
+    <t>=INDEX('찾기참조_실습'!B18:B22,MATCH(LARGE('찾기참조_실습'!D18:D22,2),'찾기참조_실습'!D18:D22,0))</t>
+  </si>
+  <si>
+    <t>60점</t>
+  </si>
+  <si>
+    <t>=HLOOKUP(60,'찾기참조_실습'!$L$8:$P$9,2,1)</t>
+  </si>
+  <si>
+    <t>동점이면 MATCH는 위에서 처음 나온 지점을 반환합니다.</t>
+  </si>
+  <si>
+    <t>HLOOKUP의 1은 점수 이하에서 가장 큰 기준값을 찾습니다. L8:P8을 오름차순으로 유지하세요.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>AbcdafF</t>
-  </si>
-  <si>
-    <t>B-1</t>
-  </si>
-  <si>
-    <t>이용석</t>
-  </si>
-  <si>
-    <t>a의 위치 SEARCH</t>
-  </si>
-  <si>
-    <t>이효리</t>
-  </si>
-  <si>
-    <t>a의 위치 FIND</t>
-  </si>
-  <si>
-    <t>3월 소고기 등급별 판매 통계</t>
-  </si>
-  <si>
-    <t>등급별 kg당 판매가</t>
-  </si>
-  <si>
-    <t>지점명</t>
-  </si>
-  <si>
-    <t>3월 판매량 (kg)</t>
-  </si>
-  <si>
-    <t>월간 판매액 (원)</t>
-  </si>
-  <si>
-    <t>금액 (원)</t>
-  </si>
-  <si>
-    <t>횡성점</t>
-  </si>
-  <si>
-    <t>국산(A++)</t>
-  </si>
-  <si>
-    <t>이천점</t>
-  </si>
-  <si>
-    <t>국산(A+)</t>
-  </si>
-  <si>
-    <t>보령점</t>
-  </si>
-  <si>
-    <t>국산(A)</t>
-  </si>
-  <si>
-    <t>제주점</t>
-  </si>
-  <si>
-    <t>미국산</t>
-  </si>
-  <si>
-    <t>부산점</t>
-  </si>
-  <si>
-    <t>호주산</t>
-  </si>
-  <si>
-    <t>3월 판매량이 가장 많은 지점</t>
-  </si>
-  <si>
-    <t>노란 칸에 수식을 입력하세요. 자세한 문제는 문제와힌트 시트에 있습니다.</t>
-  </si>
-  <si>
-    <t>학습용 전사 자료: 노트 020~021페이지. SEARCH는 M12, FIND는 M13에 입력합니다.</t>
-  </si>
-  <si>
-    <t>판매사원 이름은 사진의 판독에 따라 옮겼으며, 이 문제의 계산에는 사용하지 않습니다.</t>
-  </si>
-  <si>
-    <t>파란 칸은 정답 수식입니다. 셀을 클릭하면 수식 입력줄에서 수식을 볼 수 있습니다.</t>
-  </si>
-  <si>
-    <t>020 021 찾기 참조 함수 문제와 힌트</t>
-  </si>
-  <si>
-    <t>실습 시트에서 입력하고 정답 시트와 비교하세요. 단가·등급·비고는 13행까지 채웁니다.</t>
-  </si>
-  <si>
-    <t>번호</t>
-  </si>
-  <si>
-    <t>입력 위치</t>
-  </si>
-  <si>
-    <t>문제</t>
-  </si>
-  <si>
-    <t>힌트</t>
-  </si>
-  <si>
-    <t>첫 결과</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>G3:G13</t>
-  </si>
-  <si>
-    <t>제품코드 첫 글자로 단가를 구하세요.</t>
-  </si>
-  <si>
-    <t>VLOOKUP, LEFT</t>
-  </si>
-  <si>
-    <t>G3=10,000</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>H3:H13</t>
-  </si>
-  <si>
-    <t>점수에 따른 등급을 구하세요.</t>
-  </si>
-  <si>
-    <t>HLOOKUP, 근사값 1</t>
-  </si>
-  <si>
-    <t>H3=A</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>I3:I13</t>
-  </si>
-  <si>
-    <t>제품코드 끝 숫자가 1~4이면 슈퍼·골드·실버·브론즈를 표시하세요.</t>
-  </si>
-  <si>
-    <t>CHOOSE, RIGHT</t>
-  </si>
-  <si>
-    <t>I3=슈퍼</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>M12</t>
-  </si>
-  <si>
-    <t>K11에서 소문자 a의 위치를 대소문자 구분 없이 구하세요.</t>
-  </si>
-  <si>
-    <t>SEARCH</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>M13</t>
-  </si>
-  <si>
-    <t>K11에서 소문자 a의 위치를 대소문자를 구분하여 구하세요.</t>
-  </si>
-  <si>
-    <t>FIND</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>E18:E22</t>
-  </si>
-  <si>
-    <t>판매량 × 등급별 kg당 판매가를 구하세요.</t>
-  </si>
-  <si>
-    <t>INDEX, MATCH</t>
-  </si>
-  <si>
-    <t>E18=11,720,000</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>B25</t>
-  </si>
-  <si>
-    <t>3월 판매량이 가장 많은 지점명을 구하세요.</t>
-  </si>
-  <si>
-    <t>INDEX, MATCH, LARGE</t>
-  </si>
-  <si>
-    <t>입력 방법: 이름 상자에 G3 입력 → Enter → =로 시작하는 수식 입력 → Enter.</t>
-  </si>
-  <si>
-    <t>채우기 방법: G3:G13 선택 → 홈 → 편집 → 채우기 → 아래쪽 또는 Ctrl+D.</t>
-  </si>
-  <si>
-    <t>함수 마법사: 결과 셀 선택 → 수식 → 함수 삽입 또는 수식 입력줄 왼쪽 fx.</t>
-  </si>
-  <si>
-    <t>범위 고정: 수식 편집 중 K3:L6 선택 → F4 → $K$3:$L$6.</t>
-  </si>
-  <si>
-    <t>INDEX의 범위는 제목을 뺀 데이터입니다. MATCH의 0은 정확히 같은 값을 찾습니다.</t>
-  </si>
-  <si>
-    <t>원본 문제 ⑤의 M12는 화면 배치에 맞춰 M13으로 수정했습니다.</t>
-  </si>
-  <si>
-    <t>정답은 직접 계산하는 수식으로 저장되어 입력 자료를 바꾸면 결과도 바뀝니다.</t>
-  </si>
-  <si>
-    <t>추가 연습과 확인</t>
-  </si>
-  <si>
-    <t>연습 내용</t>
-  </si>
-  <si>
-    <t>답 입력</t>
-  </si>
-  <si>
-    <t>확인할 내용</t>
-  </si>
-  <si>
-    <t>79점의 등급</t>
-  </si>
-  <si>
-    <t>실습 시트의 점수 기준표를 HLOOKUP으로 참조</t>
-  </si>
-  <si>
-    <t>D-4의 단가</t>
-  </si>
-  <si>
-    <t>LEFT로 첫 글자를 구한 뒤 VLOOKUP 사용</t>
-  </si>
-  <si>
-    <t>D-4의 비고</t>
-  </si>
-  <si>
-    <t>RIGHT로 끝 숫자를 구한 뒤 CHOOSE 사용</t>
-  </si>
-  <si>
-    <t>두 번째 판매량 지점</t>
-  </si>
-  <si>
-    <t>LARGE의 두 번째 인수를 2로 사용</t>
-  </si>
-  <si>
-    <t>점수 60의 등급</t>
-  </si>
-  <si>
-    <t>HLOOKUP 근사값의 경계값 확인</t>
-  </si>
-  <si>
-    <t>문항</t>
-  </si>
-  <si>
-    <t>정답 수식</t>
-  </si>
-  <si>
-    <t>결과</t>
-  </si>
-  <si>
-    <t>79점</t>
-  </si>
-  <si>
-    <t>=HLOOKUP(79,'찾기참조_실습'!$L$8:$P$9,2,1)</t>
-  </si>
-  <si>
-    <t>D-4 단가</t>
-  </si>
-  <si>
-    <t>=VLOOKUP(LEFT("D-4",1),'찾기참조_실습'!$K$3:$L$6,2,0)</t>
-  </si>
-  <si>
-    <t>D-4 비고</t>
-  </si>
-  <si>
-    <t>=CHOOSE(RIGHT("D-4",1),"슈퍼","골드","실버","브론즈")</t>
-  </si>
-  <si>
-    <t>두 번째 지점</t>
-  </si>
-  <si>
-    <t>=INDEX('찾기참조_실습'!B18:B22,MATCH(LARGE('찾기참조_실습'!D18:D22,2),'찾기참조_실습'!D18:D22,0))</t>
-  </si>
-  <si>
-    <t>60점</t>
-  </si>
-  <si>
-    <t>=HLOOKUP(60,'찾기참조_실습'!$L$8:$P$9,2,1)</t>
-  </si>
-  <si>
-    <t>동점이면 MATCH는 위에서 처음 나온 지점을 반환합니다.</t>
-  </si>
-  <si>
-    <t>HLOOKUP의 1은 점수 이하에서 가장 큰 기준값을 찾습니다. L8:P8을 오름차순으로 유지하세요.</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1164,7 +1162,7 @@
       <c r="I11" s="5"/>
       <c r="J11" s="2"/>
       <c r="K11" s="15" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
@@ -1175,10 +1173,10 @@
     <row r="12" spans="1:16" ht="26.1" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D12" s="6">
         <v>9542100</v>
@@ -1194,7 +1192,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="2"/>
       <c r="K12" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L12" s="16"/>
       <c r="M12" s="5"/>
@@ -1208,7 +1206,7 @@
         <v>20</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" s="6">
         <v>6345600</v>
@@ -1224,7 +1222,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="2"/>
       <c r="K13" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L13" s="16"/>
       <c r="M13" s="5"/>
@@ -1271,14 +1269,14 @@
     <row r="16" spans="1:16" ht="26.1" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="2"/>
       <c r="G16" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="2"/>
@@ -1293,23 +1291,23 @@
     <row r="17" spans="1:16" ht="38.1" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -1323,10 +1321,10 @@
     <row r="18" spans="1:16" ht="26.1" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="D18" s="3">
         <v>200</v>
@@ -1334,7 +1332,7 @@
       <c r="E18" s="7"/>
       <c r="F18" s="2"/>
       <c r="G18" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H18" s="6">
         <v>58600</v>
@@ -1351,10 +1349,10 @@
     <row r="19" spans="1:16" ht="26.1" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="D19" s="3">
         <v>310</v>
@@ -1362,7 +1360,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="2"/>
       <c r="G19" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H19" s="6">
         <v>51200</v>
@@ -1379,10 +1377,10 @@
     <row r="20" spans="1:16" ht="26.1" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="D20" s="3">
         <v>250</v>
@@ -1390,7 +1388,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="2"/>
       <c r="G20" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H20" s="6">
         <v>45600</v>
@@ -1407,10 +1405,10 @@
     <row r="21" spans="1:16" ht="26.1" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="D21" s="3">
         <v>180</v>
@@ -1418,7 +1416,7 @@
       <c r="E21" s="7"/>
       <c r="F21" s="2"/>
       <c r="G21" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H21" s="6">
         <v>39200</v>
@@ -1435,10 +1433,10 @@
     <row r="22" spans="1:16" ht="26.1" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="D22" s="3">
         <v>220</v>
@@ -1446,7 +1444,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="2"/>
       <c r="G22" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H22" s="6">
         <v>41300</v>
@@ -1481,7 +1479,7 @@
     <row r="24" spans="1:16" ht="26.1" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
@@ -1554,9 +1552,7 @@
     </row>
     <row r="28" spans="1:16" ht="26.1" customHeight="1">
       <c r="A28" s="2"/>
-      <c r="B28" s="19" t="s">
-        <v>52</v>
-      </c>
+      <c r="B28" s="19"/>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
@@ -1592,9 +1588,7 @@
     </row>
     <row r="30" spans="1:16" ht="26.1" customHeight="1">
       <c r="A30" s="2"/>
-      <c r="B30" s="19" t="s">
-        <v>53</v>
-      </c>
+      <c r="B30" s="19"/>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
@@ -1612,9 +1606,7 @@
     </row>
     <row r="31" spans="1:16" ht="26.1" customHeight="1">
       <c r="A31" s="2"/>
-      <c r="B31" s="19" t="s">
-        <v>54</v>
-      </c>
+      <c r="B31" s="19"/>
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
       <c r="E31" s="19"/>
@@ -2162,7 +2154,7 @@
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="15" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
@@ -2173,10 +2165,10 @@
     <row r="12" spans="1:16" ht="26.1" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D12" s="6">
         <v>9542100</v>
@@ -2201,7 +2193,7 @@
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L12" s="16"/>
       <c r="M12" s="9">
@@ -2218,7 +2210,7 @@
         <v>20</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" s="6">
         <v>6345600</v>
@@ -2243,7 +2235,7 @@
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L13" s="16"/>
       <c r="M13" s="9">
@@ -2293,14 +2285,14 @@
     <row r="16" spans="1:16" ht="26.1" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="2"/>
       <c r="G16" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="2"/>
@@ -2315,23 +2307,23 @@
     <row r="17" spans="1:16" ht="38.1" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -2345,10 +2337,10 @@
     <row r="18" spans="1:16" ht="26.1" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="D18" s="3">
         <v>200</v>
@@ -2359,7 +2351,7 @@
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H18" s="6">
         <v>58600</v>
@@ -2376,10 +2368,10 @@
     <row r="19" spans="1:16" ht="26.1" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="D19" s="3">
         <v>310</v>
@@ -2390,7 +2382,7 @@
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H19" s="6">
         <v>51200</v>
@@ -2407,10 +2399,10 @@
     <row r="20" spans="1:16" ht="26.1" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="D20" s="3">
         <v>250</v>
@@ -2421,7 +2413,7 @@
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H20" s="6">
         <v>45600</v>
@@ -2438,10 +2430,10 @@
     <row r="21" spans="1:16" ht="26.1" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="D21" s="3">
         <v>180</v>
@@ -2452,7 +2444,7 @@
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H21" s="6">
         <v>39200</v>
@@ -2469,10 +2461,10 @@
     <row r="22" spans="1:16" ht="26.1" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="D22" s="3">
         <v>220</v>
@@ -2483,7 +2475,7 @@
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H22" s="6">
         <v>41300</v>
@@ -2518,7 +2510,7 @@
     <row r="24" spans="1:16" ht="26.1" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
@@ -2595,7 +2587,7 @@
     <row r="28" spans="1:16" ht="26.1" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
@@ -2633,7 +2625,7 @@
     <row r="30" spans="1:16" ht="26.1" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
@@ -2653,7 +2645,7 @@
     <row r="31" spans="1:16" ht="26.1" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
@@ -2778,7 +2770,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="38.1" customHeight="1">
       <c r="A1" s="21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -2794,7 +2786,7 @@
     </row>
     <row r="3" spans="1:5" ht="38.1" customHeight="1">
       <c r="A3" s="22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -2810,138 +2802,138 @@
     </row>
     <row r="5" spans="1:5" ht="38.1" customHeight="1">
       <c r="A5" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="D5" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>60</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="57.95" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="D6" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="E6" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="57.95" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="D7" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="E7" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="57.95" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="D8" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="E8" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="57.95" customHeight="1">
       <c r="A9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="D9" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>81</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="57.95" customHeight="1">
       <c r="A10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="D10" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>85</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="57.95" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="D11" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="E11" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="57.95" customHeight="1">
       <c r="A12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="D12" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>94</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="38.1" customHeight="1">
@@ -2960,7 +2952,7 @@
     </row>
     <row r="15" spans="1:5" ht="38.1" customHeight="1">
       <c r="A15" s="22" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
@@ -2969,7 +2961,7 @@
     </row>
     <row r="16" spans="1:5" ht="38.1" customHeight="1">
       <c r="A16" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B16" s="22"/>
       <c r="C16" s="22"/>
@@ -2978,7 +2970,7 @@
     </row>
     <row r="17" spans="1:5" ht="38.1" customHeight="1">
       <c r="A17" s="22" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
@@ -2987,7 +2979,7 @@
     </row>
     <row r="18" spans="1:5" ht="38.1" customHeight="1">
       <c r="A18" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B18" s="22"/>
       <c r="C18" s="22"/>
@@ -2996,7 +2988,7 @@
     </row>
     <row r="19" spans="1:5" ht="38.1" customHeight="1">
       <c r="A19" s="22" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>
@@ -3005,7 +2997,7 @@
     </row>
     <row r="20" spans="1:5" ht="38.1" customHeight="1">
       <c r="A20" s="22" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
@@ -3014,7 +3006,7 @@
     </row>
     <row r="21" spans="1:5" ht="38.1" customHeight="1">
       <c r="A21" s="22" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
@@ -3023,7 +3015,7 @@
     </row>
     <row r="22" spans="1:5" ht="38.1" customHeight="1">
       <c r="A22" s="22" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
@@ -3107,7 +3099,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="32.1" customHeight="1">
       <c r="A1" s="21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -3123,68 +3115,68 @@
     </row>
     <row r="3" spans="1:5" ht="32.1" customHeight="1">
       <c r="A3" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>105</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="32.1" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" ht="32.1" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="32.1" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="32.1" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" ht="32.1" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -3205,23 +3197,23 @@
     </row>
     <row r="11" spans="1:5" ht="32.1" customHeight="1">
       <c r="A11" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>116</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>118</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5" ht="60" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C12" s="1" t="str">
         <f>HLOOKUP(79,찾기참조_실습!$L$8:$P$9,2,1)</f>
@@ -3232,10 +3224,10 @@
     </row>
     <row r="13" spans="1:5" ht="60" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C13" s="14">
         <f>VLOOKUP(LEFT("D-4",1),찾기참조_실습!$K$3:$L$6,2,0)</f>
@@ -3246,10 +3238,10 @@
     </row>
     <row r="14" spans="1:5" ht="60" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C14" s="1" t="str">
         <f>CHOOSE(RIGHT("D-4",1),"슈퍼","골드","실버","브론즈")</f>
@@ -3260,10 +3252,10 @@
     </row>
     <row r="15" spans="1:5" ht="60" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C15" s="1" t="str">
         <f>INDEX(찾기참조_실습!B18:B22,MATCH(LARGE(찾기참조_실습!D18:D22,2),찾기참조_실습!D18:D22,0))</f>
@@ -3274,10 +3266,10 @@
     </row>
     <row r="16" spans="1:5" ht="60" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="1" t="str">
         <f>HLOOKUP(60,찾기참조_실습!$L$8:$P$9,2,1)</f>
@@ -3302,7 +3294,7 @@
     </row>
     <row r="19" spans="1:5" ht="32.1" customHeight="1">
       <c r="A19" s="22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>

--- a/교재/엑셀교재v2/020-021_찾기참조함수_실습.xlsx
+++ b/교재/엑셀교재v2/020-021_찾기참조함수_실습.xlsx
@@ -533,7 +533,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -591,6 +591,24 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -838,7 +856,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:16" ht="26.1" customHeight="1">
+    <row r="2" spans="1:16" ht="56" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="4" t="s">
         <v>0</v>
@@ -855,14 +873,23 @@
       <c r="F2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>7</v>
+      <c r="G2" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단가
+(VLOOKUP, LEFT 사용)</t>
+        </is>
+      </c>
+      <c r="H2" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">등급
+(HLOOKUP 사용)</t>
+        </is>
+      </c>
+      <c r="I2" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고
+(CHOOSE, RIGHT 사용)</t>
+        </is>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="4" t="s">
@@ -1288,7 +1315,7 @@
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
     </row>
-    <row r="17" spans="1:16" ht="38.1" customHeight="1">
+    <row r="17" spans="1:16" ht="56" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="4" t="s">
         <v>36</v>
@@ -1299,8 +1326,11 @@
       <c r="D17" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>38</v>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">월간 판매액 (원)
+(INDEX, MATCH 사용)</t>
+        </is>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="4" t="s">
@@ -1476,10 +1506,12 @@
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
     </row>
-    <row r="24" spans="1:16" ht="26.1" customHeight="1">
+    <row r="24" spans="1:16" ht="56" customHeight="1">
       <c r="A24" s="2"/>
-      <c r="B24" s="16" t="s">
-        <v>50</v>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3월 판매량이 가장 많은 지점 (INDEX, MATCH, LARGE 함수 사용)</t>
+        </is>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
@@ -1552,7 +1584,11 @@
     </row>
     <row r="28" spans="1:16" ht="26.1" customHeight="1">
       <c r="A28" s="2"/>
-      <c r="B28" s="19"/>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">각 문제에 지정된 함수를 사용하세요. 단가·등급·비고는 3~13행, 월간 판매액은 18~22행에 입력하세요.</t>
+        </is>
+      </c>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
@@ -1749,7 +1785,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:16" ht="26.1" customHeight="1">
+    <row r="2" spans="1:16" ht="56" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="4" t="s">
         <v>0</v>
@@ -1766,14 +1802,23 @@
       <c r="F2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>7</v>
+      <c r="G2" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단가
+(VLOOKUP, LEFT 사용)</t>
+        </is>
+      </c>
+      <c r="H2" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">등급
+(HLOOKUP 사용)</t>
+        </is>
+      </c>
+      <c r="I2" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고
+(CHOOSE, RIGHT 사용)</t>
+        </is>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="4" t="s">
@@ -2304,7 +2349,7 @@
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
     </row>
-    <row r="17" spans="1:16" ht="38.1" customHeight="1">
+    <row r="17" spans="1:16" ht="56" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="4" t="s">
         <v>36</v>
@@ -2315,8 +2360,11 @@
       <c r="D17" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>38</v>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">월간 판매액 (원)
+(INDEX, MATCH 사용)</t>
+        </is>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="4" t="s">
@@ -2507,10 +2555,12 @@
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
     </row>
-    <row r="24" spans="1:16" ht="26.1" customHeight="1">
+    <row r="24" spans="1:16" ht="56" customHeight="1">
       <c r="A24" s="2"/>
-      <c r="B24" s="16" t="s">
-        <v>50</v>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3월 판매량이 가장 많은 지점 (INDEX, MATCH, LARGE 함수 사용)</t>
+        </is>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
@@ -2586,8 +2636,10 @@
     </row>
     <row r="28" spans="1:16" ht="26.1" customHeight="1">
       <c r="A28" s="2"/>
-      <c r="B28" s="19" t="s">
-        <v>53</v>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">각 문제에 지정된 함수를 사용하세요. 단가·등급·비고는 3~13행, 월간 판매액은 18~22행에 입력하세요.</t>
+        </is>
       </c>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
@@ -2810,8 +2862,10 @@
       <c r="C5" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>59</v>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용할 함수·조건</t>
+        </is>
       </c>
       <c r="E5" s="11" t="s">
         <v>60</v>
@@ -2824,8 +2878,10 @@
       <c r="B6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>63</v>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VLOOKUP, LEFT 함수를 사용하여 제품코드 첫 글자로 단가를 구하세요.</t>
+        </is>
       </c>
       <c r="D6" s="12" t="s">
         <v>64</v>
@@ -2841,8 +2897,10 @@
       <c r="B7" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>68</v>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HLOOKUP 함수를 사용하여 점수에 따른 등급을 구하세요.</t>
+        </is>
       </c>
       <c r="D7" s="12" t="s">
         <v>69</v>
@@ -2858,8 +2916,10 @@
       <c r="B8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>73</v>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHOOSE, RIGHT 함수를 사용하여 제품코드 끝 숫자 1~4에 따라 슈퍼·골드·실버·브론즈를 표시하세요.</t>
+        </is>
       </c>
       <c r="D8" s="12" t="s">
         <v>74</v>
@@ -2875,8 +2935,10 @@
       <c r="B9" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>78</v>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEARCH 함수를 사용하여 K11에서 소문자 a의 위치를 대소문자 구분 없이 구하세요.</t>
+        </is>
       </c>
       <c r="D9" s="12" t="s">
         <v>79</v>
@@ -2892,8 +2954,10 @@
       <c r="B10" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>82</v>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIND 함수를 사용하여 K11에서 소문자 a의 위치를 대소문자를 구분하여 구하세요.</t>
+        </is>
       </c>
       <c r="D10" s="12" t="s">
         <v>83</v>
@@ -2909,8 +2973,10 @@
       <c r="B11" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>86</v>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INDEX, MATCH 함수를 사용하여 판매량 × 등급별 kg당 판매가로 월간 판매액을 구하세요.</t>
+        </is>
       </c>
       <c r="D11" s="12" t="s">
         <v>87</v>
@@ -2926,8 +2992,10 @@
       <c r="B12" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>91</v>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INDEX, MATCH, LARGE 함수를 사용하여 3월 판매량이 가장 많은 지점명을 구하세요.</t>
+        </is>
       </c>
       <c r="D12" s="12" t="s">
         <v>92</v>
@@ -3120,8 +3188,10 @@
       <c r="B3" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>103</v>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용할 함수·조건</t>
+        </is>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -3164,8 +3234,10 @@
         <v>110</v>
       </c>
       <c r="B7" s="13"/>
-      <c r="C7" s="1" t="s">
-        <v>111</v>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INDEX, MATCH, LARGE 함수를 사용하여 판매량이 두 번째로 많은 지점명을 구하세요.</t>
+        </is>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
